--- a/www/ig/fhir/mesures/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/www/ig/fhir/mesures/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$105</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4437" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4055" uniqueCount="673">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T08:41:57+00:00</t>
+    <t>2026-02-18T13:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,11 +656,24 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
+    <t>Autres ressources pertinentes *du dossier patient*</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t>MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement}
 </t>
+  </si>
+  <si>
+    <t>Motif de la mesure</t>
+  </si>
+  <si>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -1321,7 +1334,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -1914,43 +1927,10 @@
     <t>Need to be able to identify the target population for proper interpretation.</t>
   </si>
   <si>
-    <t>JDV_J148-ReferenceRangeAppliesTo-CISIS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J148-ReferenceRangeAppliesTo-CISIS/FHIR/JDV-J148-ReferenceRangeAppliesTo-CISIS</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.text</t>
+    <t>Codes identifying the population the reference range applies to.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -2450,20 +2430,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP115"/>
+  <dimension ref="A1:AP105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.09375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="56.09375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.38671875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.26953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.26953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="223.14453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2472,28 +2452,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="112.42578125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.5859375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4754,7 +4734,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>122</v>
@@ -4780,46 +4760,44 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="B20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>114</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O20" t="s" s="2">
         <v>210</v>
       </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4867,7 +4845,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4891,7 +4869,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4902,14 +4880,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4922,23 +4900,25 @@
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4987,7 +4967,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4999,22 +4979,22 @@
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>220</v>
+        <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -5022,14 +5002,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5048,17 +5028,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5107,7 +5087,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5122,19 +5102,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5142,14 +5122,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5168,18 +5148,18 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5227,7 +5207,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5242,16 +5222,16 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5262,46 +5242,44 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5325,11 +5303,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5347,13 +5327,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -5362,30 +5342,30 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5396,31 +5376,31 @@
         <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>252</v>
+        <v>173</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5445,35 +5425,35 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -5482,19 +5462,19 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5502,14 +5482,12 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5518,7 +5496,7 @@
         <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>94</v>
@@ -5530,19 +5508,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5570,28 +5548,26 @@
         <v>177</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5615,35 +5591,37 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -5652,16 +5630,20 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>108</v>
+        <v>257</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5685,13 +5667,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5709,19 +5691,19 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5733,10 +5715,10 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>111</v>
+        <v>264</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5744,21 +5726,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5770,17 +5752,15 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5817,31 +5797,31 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5864,46 +5844,44 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>115</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>116</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5939,19 +5917,19 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>121</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5963,7 +5941,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5972,10 +5950,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>276</v>
+        <v>111</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5984,12 +5962,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5997,31 +5975,35 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>108</v>
+        <v>274</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6069,19 +6051,19 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>110</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6090,10 +6072,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6104,21 +6086,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -6130,17 +6112,15 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -6177,31 +6157,31 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6224,52 +6204,50 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>115</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>116</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>82</v>
@@ -6299,31 +6277,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>121</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6332,10 +6310,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>290</v>
+        <v>111</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6344,12 +6322,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6357,13 +6335,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
@@ -6372,24 +6350,26 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>82</v>
@@ -6431,7 +6411,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6452,10 +6432,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6466,10 +6446,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6477,13 +6457,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6492,24 +6472,24 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6551,7 +6531,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6572,10 +6552,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6584,12 +6564,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6597,13 +6577,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6612,24 +6592,24 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6671,7 +6651,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6692,10 +6672,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6706,10 +6686,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6732,19 +6712,17 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6793,7 +6771,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6814,10 +6792,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6828,10 +6806,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6854,19 +6832,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>322</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6915,7 +6893,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6936,10 +6914,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6950,24 +6928,24 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6976,19 +6954,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7013,13 +6991,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -7037,10 +7015,10 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>93</v>
@@ -7052,62 +7030,66 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>108</v>
+        <v>341</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -7131,13 +7113,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7155,10 +7137,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>110</v>
+        <v>339</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -7167,44 +7149,44 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>111</v>
+        <v>350</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7216,17 +7198,15 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7263,31 +7243,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7310,18 +7290,18 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>81</v>
@@ -7333,23 +7313,21 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>270</v>
+        <v>115</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>271</v>
+        <v>116</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7385,9 +7363,11 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7395,7 +7375,7 @@
         <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>274</v>
+        <v>121</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7407,7 +7387,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7416,10 +7396,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>276</v>
+        <v>111</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7430,14 +7410,12 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7446,7 +7424,7 @@
         <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7461,16 +7439,16 @@
         <v>151</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7507,19 +7485,17 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7540,10 +7516,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7554,18 +7530,20 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="B43" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C43" s="2"/>
+      <c r="C43" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -7577,19 +7555,23 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>108</v>
+        <v>274</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7637,19 +7619,19 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>110</v>
+        <v>278</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7658,10 +7640,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7672,21 +7654,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7698,17 +7680,15 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7745,31 +7725,31 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7792,21 +7772,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7815,29 +7795,27 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>283</v>
+        <v>115</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>284</v>
+        <v>116</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>82</v>
@@ -7867,31 +7845,31 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>288</v>
+        <v>121</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7900,10 +7878,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>290</v>
+        <v>111</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7914,10 +7892,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7925,7 +7903,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>93</v>
@@ -7940,24 +7918,26 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>82</v>
@@ -7999,7 +7979,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8020,10 +8000,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8034,10 +8014,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8045,7 +8025,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -8060,24 +8040,24 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -8119,7 +8099,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8140,10 +8120,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8154,10 +8134,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8165,7 +8145,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8180,24 +8160,24 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8239,7 +8219,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8260,10 +8240,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8274,10 +8254,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8300,19 +8280,17 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8361,7 +8339,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8382,10 +8360,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8396,10 +8374,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8422,19 +8400,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>322</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8483,7 +8461,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8504,10 +8482,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8518,10 +8496,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8529,13 +8507,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
@@ -8544,19 +8522,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>373</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>374</v>
+        <v>332</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>375</v>
+        <v>333</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>376</v>
+        <v>334</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>377</v>
+        <v>335</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8605,7 +8583,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8620,30 +8598,30 @@
         <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>379</v>
+        <v>337</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>380</v>
+        <v>338</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8651,13 +8629,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -8666,18 +8644,20 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8725,13 +8705,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8740,19 +8720,19 @@
         <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8760,21 +8740,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8786,20 +8766,18 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>394</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8847,13 +8825,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8862,19 +8840,19 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>396</v>
+        <v>349</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8882,24 +8860,24 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -8908,19 +8886,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8969,59 +8947,59 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK54" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -9030,18 +9008,20 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>129</v>
+        <v>405</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9089,34 +9069,34 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AK55" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AG55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9124,10 +9104,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9138,7 +9118,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -9150,18 +9130,18 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>420</v>
+        <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9209,13 +9189,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -9224,19 +9204,19 @@
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9244,10 +9224,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9258,10 +9238,10 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
@@ -9270,19 +9250,17 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9319,65 +9297,65 @@
         <v>82</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AC57" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
@@ -9392,19 +9370,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9441,19 +9419,17 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9462,7 +9438,7 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9471,59 +9447,65 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>107</v>
+        <v>433</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>108</v>
+        <v>434</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9571,7 +9553,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>110</v>
+        <v>432</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9580,47 +9562,47 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>111</v>
+        <v>442</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9632,17 +9614,15 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9679,31 +9659,31 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9726,46 +9706,44 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>448</v>
+        <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>449</v>
+        <v>115</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>450</v>
+        <v>116</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9801,31 +9779,31 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>453</v>
+        <v>121</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9834,10 +9812,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>455</v>
+        <v>111</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9846,12 +9824,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9859,39 +9837,39 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>173</v>
+        <v>452</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="O62" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q62" t="s" s="2">
-        <v>461</v>
-      </c>
+      <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9911,13 +9889,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>462</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9935,7 +9913,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9956,10 +9934,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9970,10 +9948,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9981,37 +9959,39 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q63" s="2"/>
+      <c r="Q63" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="R63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10031,13 +10011,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -10055,7 +10035,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10076,10 +10056,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10088,12 +10068,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10116,24 +10096,24 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>480</v>
+        <v>82</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>82</v>
@@ -10175,7 +10155,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10184,7 +10164,7 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -10196,10 +10176,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10208,12 +10188,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10236,26 +10216,24 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>82</v>
@@ -10297,7 +10275,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10306,7 +10284,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -10318,10 +10296,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10330,12 +10308,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10343,7 +10321,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>93</v>
@@ -10355,29 +10333,29 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>252</v>
+        <v>173</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>82</v>
@@ -10395,13 +10373,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10419,7 +10397,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10428,7 +10406,7 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10440,10 +10418,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>196</v>
+        <v>477</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10452,12 +10430,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10471,7 +10449,7 @@
         <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>82</v>
@@ -10480,16 +10458,20 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>108</v>
+        <v>497</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10513,13 +10495,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10537,7 +10519,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>110</v>
+        <v>496</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10546,10 +10528,10 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10558,10 +10540,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>111</v>
+        <v>504</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10572,21 +10554,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10598,17 +10580,15 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10645,31 +10625,31 @@
         <v>82</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10692,14 +10672,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10715,23 +10695,21 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>270</v>
+        <v>115</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>271</v>
+        <v>116</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10767,19 +10745,19 @@
         <v>82</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>274</v>
+        <v>121</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10791,7 +10769,7 @@
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10800,10 +10778,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>276</v>
+        <v>111</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10814,10 +10792,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10828,7 +10806,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10837,19 +10815,23 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>108</v>
+        <v>274</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10897,19 +10879,19 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>110</v>
+        <v>278</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10918,10 +10900,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10932,21 +10914,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10958,17 +10940,15 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -11005,31 +10985,31 @@
         <v>82</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11052,21 +11032,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11075,23 +11055,21 @@
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>283</v>
+        <v>115</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>284</v>
+        <v>116</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11127,31 +11105,31 @@
         <v>82</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>288</v>
+        <v>121</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11160,10 +11138,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>290</v>
+        <v>111</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11174,10 +11152,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11185,7 +11163,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>93</v>
@@ -11200,18 +11178,20 @@
         <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11259,7 +11239,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11280,10 +11260,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11294,10 +11274,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11305,7 +11285,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>93</v>
@@ -11320,18 +11300,18 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11379,7 +11359,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11400,10 +11380,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11414,10 +11394,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11425,7 +11405,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>93</v>
@@ -11440,17 +11420,17 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11499,7 +11479,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11520,10 +11500,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11534,10 +11514,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11560,19 +11540,17 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11621,7 +11599,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11642,10 +11620,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11656,10 +11634,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11682,19 +11660,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>107</v>
+        <v>322</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11743,7 +11721,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11764,10 +11742,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11778,21 +11756,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11801,22 +11779,22 @@
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>514</v>
+        <v>332</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>515</v>
+        <v>333</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>516</v>
+        <v>334</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>517</v>
+        <v>335</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11841,11 +11819,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11863,13 +11843,13 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>512</v>
+        <v>336</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
@@ -11881,31 +11861,31 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>520</v>
+        <v>337</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>521</v>
+        <v>338</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11924,19 +11904,19 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>524</v>
+        <v>256</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11961,13 +11941,11 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11985,7 +11963,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12003,27 +11981,27 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12034,7 +12012,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -12046,18 +12024,20 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>252</v>
+        <v>528</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="O80" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="M80" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -12081,13 +12061,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12105,13 +12085,13 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
@@ -12123,27 +12103,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>540</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12166,20 +12146,18 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -12206,10 +12184,10 @@
         <v>163</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12227,7 +12205,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12245,27 +12223,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12288,18 +12266,20 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>551</v>
+        <v>256</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12323,13 +12303,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12347,7 +12327,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12365,27 +12345,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>558</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12399,7 +12379,7 @@
         <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>82</v>
@@ -12408,16 +12388,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12467,7 +12447,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12485,27 +12465,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12516,10 +12496,10 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12528,20 +12508,18 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12589,45 +12567,45 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="AG84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM84" t="s" s="2">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>82</v>
+        <v>571</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12638,7 +12616,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12650,16 +12628,20 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>107</v>
+        <v>573</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>108</v>
+        <v>574</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12707,19 +12689,19 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>110</v>
+        <v>572</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12728,10 +12710,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>111</v>
+        <v>580</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12742,21 +12724,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12768,17 +12750,15 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12827,19 +12807,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12862,14 +12842,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>580</v>
+        <v>113</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12882,26 +12862,24 @@
         <v>82</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>581</v>
+        <v>115</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>582</v>
+        <v>116</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O87" t="s" s="2">
-        <v>210</v>
-      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12949,7 +12927,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>583</v>
+        <v>121</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12973,7 +12951,7 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12984,42 +12962,46 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>82</v>
+        <v>584</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="M88" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
+      <c r="N88" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -13067,19 +13049,19 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>588</v>
+        <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -13088,10 +13070,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>590</v>
+        <v>196</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13102,10 +13084,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13128,13 +13110,13 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13185,7 +13167,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13194,7 +13176,7 @@
         <v>93</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>105</v>
@@ -13206,7 +13188,7 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>594</v>
@@ -13246,7 +13228,7 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>252</v>
+        <v>589</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>596</v>
@@ -13254,12 +13236,8 @@
       <c r="M90" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="N90" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>599</v>
-      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13283,13 +13261,13 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>600</v>
+        <v>82</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>601</v>
+        <v>82</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13316,7 +13294,7 @@
         <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>82</v>
+        <v>592</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>105</v>
@@ -13325,13 +13303,13 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>602</v>
+        <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>521</v>
+        <v>598</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13342,10 +13320,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13356,7 +13334,7 @@
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13368,19 +13346,19 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13405,13 +13383,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>244</v>
+        <v>177</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13429,13 +13407,13 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
@@ -13447,13 +13425,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13464,10 +13442,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13478,7 +13456,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -13490,16 +13468,20 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>108</v>
+        <v>609</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>610</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>612</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13523,13 +13505,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>82</v>
+        <v>613</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13547,31 +13529,31 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>110</v>
+        <v>608</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>111</v>
+        <v>525</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13582,21 +13564,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13608,18 +13590,18 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>114</v>
+        <v>616</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>115</v>
+        <v>617</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>618</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" t="s" s="2">
+        <v>619</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
@@ -13655,31 +13637,31 @@
         <v>82</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>121</v>
+        <v>615</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -13691,7 +13673,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>111</v>
+        <v>620</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13702,10 +13684,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13716,7 +13698,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13725,23 +13707,19 @@
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>270</v>
+        <v>622</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13789,13 +13767,13 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>274</v>
+        <v>621</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
@@ -13810,10 +13788,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>275</v>
+        <v>593</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>276</v>
+        <v>624</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13824,10 +13802,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13838,7 +13816,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13847,18 +13825,20 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>107</v>
+        <v>626</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>108</v>
+        <v>627</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>628</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>629</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13907,19 +13887,19 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>110</v>
+        <v>625</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -13928,10 +13908,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>82</v>
+        <v>630</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>111</v>
+        <v>631</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13942,14 +13922,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>615</v>
+        <v>632</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>615</v>
+        <v>632</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13965,19 +13945,19 @@
         <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>114</v>
+        <v>633</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>115</v>
+        <v>634</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>116</v>
+        <v>635</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>117</v>
+        <v>636</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14015,19 +13995,19 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>121</v>
+        <v>632</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14039,7 +14019,7 @@
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -14048,10 +14028,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>82</v>
+        <v>630</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>111</v>
+        <v>637</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14060,12 +14040,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14073,13 +14053,13 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>82</v>
@@ -14088,19 +14068,19 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>135</v>
+        <v>573</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>283</v>
+        <v>639</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>284</v>
+        <v>639</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>285</v>
+        <v>640</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>286</v>
+        <v>641</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14149,19 +14129,19 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>288</v>
+        <v>638</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>105</v>
+        <v>642</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -14170,10 +14150,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>289</v>
+        <v>643</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>290</v>
+        <v>644</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14184,10 +14164,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>617</v>
+        <v>645</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>617</v>
+        <v>645</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14207,20 +14187,18 @@
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>293</v>
+        <v>108</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -14269,7 +14247,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>296</v>
+        <v>110</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14281,7 +14259,7 @@
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14290,10 +14268,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>298</v>
+        <v>111</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14304,21 +14282,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>618</v>
+        <v>646</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>618</v>
+        <v>646</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14327,21 +14305,21 @@
         <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>301</v>
+        <v>115</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14389,19 +14367,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>305</v>
+        <v>121</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14410,10 +14388,10 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>307</v>
+        <v>111</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14424,43 +14402,45 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>619</v>
+        <v>647</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>619</v>
+        <v>647</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>82</v>
+        <v>584</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>310</v>
+        <v>585</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O100" t="s" s="2">
-        <v>312</v>
+        <v>214</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14509,19 +14489,19 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>313</v>
+        <v>587</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14530,10 +14510,10 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14542,12 +14522,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14555,13 +14535,13 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>82</v>
@@ -14570,19 +14550,19 @@
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>318</v>
+        <v>256</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>319</v>
+        <v>649</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>320</v>
+        <v>650</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>321</v>
+        <v>651</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>322</v>
+        <v>652</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14607,13 +14587,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14631,10 +14611,10 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>323</v>
+        <v>648</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>93</v>
@@ -14649,27 +14629,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>82</v>
+        <v>653</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
-        <v>621</v>
+        <v>654</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>621</v>
+        <v>654</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14683,7 +14663,7 @@
         <v>93</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>82</v>
@@ -14692,19 +14672,19 @@
         <v>94</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>107</v>
+        <v>655</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>328</v>
+        <v>656</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>329</v>
+        <v>657</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>330</v>
+        <v>658</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>331</v>
+        <v>436</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14729,13 +14709,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>82</v>
+        <v>659</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>82</v>
+        <v>660</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14753,7 +14733,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>332</v>
+        <v>654</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14762,7 +14742,7 @@
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>82</v>
+        <v>661</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14771,27 +14751,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>82</v>
+        <v>662</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>333</v>
+        <v>441</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>334</v>
+        <v>442</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
-        <v>622</v>
+        <v>663</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>622</v>
+        <v>663</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14805,7 +14785,7 @@
         <v>93</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>82</v>
@@ -14814,17 +14794,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>623</v>
+        <v>256</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>624</v>
+        <v>664</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>665</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>666</v>
+      </c>
       <c r="O103" t="s" s="2">
-        <v>626</v>
+        <v>500</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14849,13 +14831,13 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14873,7 +14855,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>622</v>
+        <v>663</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14882,7 +14864,7 @@
         <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>82</v>
+        <v>667</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>105</v>
@@ -14894,10 +14876,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>627</v>
+        <v>504</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14908,21 +14890,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>628</v>
+        <v>668</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>628</v>
+        <v>668</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14934,16 +14916,20 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>629</v>
+        <v>518</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
       </c>
@@ -14967,13 +14953,13 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>82</v>
+        <v>669</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14991,13 +14977,13 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>628</v>
+        <v>668</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
@@ -15009,27 +14995,27 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>589</v>
+        <v>524</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>631</v>
+        <v>525</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>632</v>
+        <v>670</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>632</v>
+        <v>670</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15049,21 +15035,23 @@
         <v>82</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>633</v>
+        <v>83</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>634</v>
+        <v>671</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>635</v>
+        <v>672</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -15111,7 +15099,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>632</v>
+        <v>670</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15132,1242 +15120,30 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>637</v>
+        <v>579</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>638</v>
+        <v>580</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="O106" s="2"/>
-      <c r="P106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="P107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
-      <c r="P108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O109" s="2"/>
-      <c r="P109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="P111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="P112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="P113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="P114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="P115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP115" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP115">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AP105">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI114">
+  <conditionalFormatting sqref="A2:AI104">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
